--- a/PGO_V1.0_core_concepts_2026-03-05.xlsx
+++ b/PGO_V1.0_core_concepts_2026-03-05.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanninisato/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4732894-2FD7-2B4B-8612-83D1C920D50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C86A90F-59DE-374B-8F21-592F6E40593E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3760" yWindow="2960" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PGO_V1.0_core_concepts" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="113">
   <si>
     <t>Concept Label Text</t>
   </si>
@@ -56,12 +56,6 @@
   </si>
   <si>
     <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>Source attribution: Ontology for Biomedical Investigations (OBI)
- licence: CC BY 4.0 
- URL licence: https://creativecommons.org/licenses/by/4.0/- 
- Definition accessed on the date: 2025-06-02</t>
   </si>
   <si>
     <t>https://ontology.iedb.org/ontology/OBI:0000070</t>
@@ -86,12 +80,6 @@
     <t>[C16342]</t>
   </si>
   <si>
-    <t>Source attribution: NCI-Thesaurus (NCIT) 
- licence: CC BY 4.0 
- URL licence: https://creativecommons.org/licenses/by/4.0/deed.en- 
-Definition accessed on the date: 2025-05-30</t>
-  </si>
-  <si>
     <t>https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C16342</t>
   </si>
   <si>
@@ -108,12 +96,6 @@
     <t>[C70699]</t>
   </si>
   <si>
-    <t>Source attribution: NCI-Thesaurus (NCIT) 
-licence: CC BY 4.0 
- URL licence: https://creativecommons.org/licenses/by/4.0/deed.en- 
-Definition accessed on the date: 2025-05-30</t>
-  </si>
-  <si>
     <t>https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C70699</t>
   </si>
   <si>
@@ -163,12 +145,6 @@
   </si>
   <si>
     <t>[C70777]</t>
-  </si>
-  <si>
-    <t>Source attribution: NCI-Thesaurus (NCIT) 
- licence: CC BY 4.0 
- URL licence: https://creativecommons.org/licenses/by/4.0/deed.en- 
- Definition accessed on the date: 2025-05-30</t>
   </si>
   <si>
     <t>https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C70777</t>
@@ -223,12 +199,6 @@
   </si>
   <si>
     <t>[D004194]</t>
-  </si>
-  <si>
-    <t>Source attribution: National Library of Medicine (NLM) - MESH 
- licence: Free access with clear attribution to NLM. 
- URL licence: https://www.nlm.nih.gov/databases/download/terms_and_conditions_mesh.html- 
-Definition accessed on the date: 2025-05-30</t>
   </si>
   <si>
     <t>https://meshb.nlm.nih.gov/record/ui?ui=D004194</t>
@@ -254,12 +224,6 @@
     <t>[23888]</t>
   </si>
   <si>
-    <t>Source attribution: Chemical Entities of Biological Interest (ChEBI) 
- licence: CC BY 4.0 
- URL licence: https://creativecommons.org/licenses/by/4.0/deed.en- 
- Definition accessed on the date: 2025-06-09</t>
-  </si>
-  <si>
     <t>https://www.ebi.ac.uk/chebi/searchId.do?chebiId=CHEBI:23888</t>
   </si>
   <si>
@@ -329,9 +293,6 @@
     <t>[0326]</t>
   </si>
   <si>
-    <t>Source attribution: Molecular Interactions (MI) - licence: CC BY 4.0 - URL licence: https://github.com/HUPO-PSI/psi-mi-CV/blob/master/LICENSE- Definition accessed on the date: 2025-06-09</t>
-  </si>
-  <si>
     <t>https://www.ebi.ac.uk/ols4/ontologies/mi/classes/http%253A%252F%252Fpurl.obolibrary.org%252Fobo%252FMI_0326</t>
   </si>
   <si>
@@ -348,12 +309,6 @@
   </si>
   <si>
     <t>[Taxon]</t>
-  </si>
-  <si>
-    <t>Source attribution: UniProt 
- licence: CC BY 4.0 
- URL licence: https://creativecommons.org/licenses/by/4.0/- 
- Definition accessed on the date: 2025-06-09</t>
   </si>
   <si>
     <t>https://purl.uniprot.org/html/index-en.html#Taxon</t>
@@ -391,20 +346,78 @@
     <t>[unit]</t>
   </si>
   <si>
+    <t>https://qudt.org/vocab/unit/</t>
+  </si>
+  <si>
+    <t>https://qudt.org/schema/qudt/Unit
+https://www.qudt.org/doc/DOC_VOCAB-UNITS.html</t>
+  </si>
+  <si>
+    <t>Recommended Definition Text</t>
+  </si>
+  <si>
+    <t>Source attribution: NCI-Thesaurus (NCIT) 
+ licence: CC BY 4.0 
+ URL licence: https://creativecommons.org/licenses/by/4.0/deed.en
+Definition accessed on the date: 2025-05-30</t>
+  </si>
+  <si>
+    <t>Source attribution: Ontology for Biomedical Investigations (OBI)
+ licence: CC BY 4.0 
+ URL licence: https://creativecommons.org/licenses/by/4.0/deed.en 
+ Definition accessed on the date: 2025-06-02</t>
+  </si>
+  <si>
+    <t>Source attribution: NCI-Thesaurus (NCIT) 
+licence: CC BY 4.0 
+ URL licence: https://creativecommons.org/licenses/by/4.0/deed.en
+Definition accessed on the date: 2025-05-30</t>
+  </si>
+  <si>
+    <t>Source attribution: NCI-Thesaurus (NCIT) 
+ licence: CC BY 4.0 
+ URL licence: https://creativecommons.org/licenses/by/4.0/deed.en 
+ Definition accessed on the date: 2025-05-30</t>
+  </si>
+  <si>
+    <t>Source attribution: NCI-Thesaurus (NCIT) 
+ licence: CC BY 4.0 
+ URL licence: https://creativecommons.org/licenses/by/4.0/deed.en
+ Definition accessed on the date: 2025-05-30</t>
+  </si>
+  <si>
+    <t>Source attribution: National Library of Medicine (NLM) - MESH 
+ licence: Free access with clear attribution to NLM. 
+ URL licence: https://www.nlm.nih.gov/databases/download/terms_and_conditions_mesh.html
+Definition accessed on the date: 2025-05-30</t>
+  </si>
+  <si>
+    <t>Source attribution: Chemical Entities of Biological Interest (ChEBI) 
+ licence: CC BY 4.0 
+ URL licence: https://creativecommons.org/licenses/by/4.0/deed.en
+ Definition accessed on the date: 2025-06-09</t>
+  </si>
+  <si>
+    <t>Source attribution: Molecular Interactions (MI) - licence: CC BY 4.0 - URL licence: https://github.com/HUPO-PSI/psi-mi-CV/blob/master/LICENSE
+Definition accessed on the date: 2025-06-09</t>
+  </si>
+  <si>
+    <t>Source attribution: UniProt 
+ licence: CC BY 4.0 
+ URL licence: https://creativecommons.org/licenses/by/4.0/deed.en
+ Definition accessed on the date: 2025-06-09</t>
+  </si>
+  <si>
+    <t>Source attribution: NCI-Thesaurus (NCIT) 
+ licence: CC BY 4.0 
+ URL licence: https://creativecommons.org/licenses/by/4.0/deed.en 
+Definition accessed on the date: 2025-05-30</t>
+  </si>
+  <si>
     <t>Source attribution: QUDT 
  licence: CC BY 4.0 
-URL licence: https://creativecommons.org/licenses/by/4.0/deed.en- 
+URL licence: https://creativecommons.org/licenses/by/4.0/deed.en
  Definition accessed on the date: 2025-09-09</t>
-  </si>
-  <si>
-    <t>https://qudt.org/vocab/unit/</t>
-  </si>
-  <si>
-    <t>https://qudt.org/schema/qudt/Unit
-https://www.qudt.org/doc/DOC_VOCAB-UNITS.html</t>
-  </si>
-  <si>
-    <t>Recommended Definition Text</t>
   </si>
 </sst>
 </file>
@@ -513,7 +526,21 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -544,20 +571,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -572,17 +585,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A9B46AF-89D1-054A-8B37-B33B092E5C25}" name="Table1" displayName="Table1" ref="A1:H18" totalsRowShown="0" headerRowDxfId="9" dataDxfId="0" headerRowBorderDxfId="10" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A9B46AF-89D1-054A-8B37-B33B092E5C25}" name="Table1" displayName="Table1" ref="A1:H18" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
   <autoFilter ref="A1:H18" xr:uid="{9A9B46AF-89D1-054A-8B37-B33B092E5C25}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{0461AE8F-0F46-9B48-ACB1-DA86ED4AED15}" name="Concept Label Text" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{47B64B06-AAFE-8543-9A00-F21FE128444B}" name="Recommended Definition Text" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{98E3D70A-2524-644A-852E-56E9C2486A77}" name="Source Definition" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{020D7F23-A82E-534F-AC8B-607876DDDA5B}" name="Source Definition ID" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{8827E3BD-F359-2D4D-93BA-19D1AAC81AA3}" name="Date approval of experts recommendations by the PGO steering committee [YYYY-MM-DD]" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{6C8AF982-573E-4F42-A3ED-E79F3399089C}" name="Attribution text" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{51B7F749-BA2F-5042-B34C-A4A1DB0A5929}" name="URL recommended definition" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{2D7BA063-8095-9640-A452-EA7ECF12740E}" name="Examples of sources (these are  not yet  recommended sources)" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{0461AE8F-0F46-9B48-ACB1-DA86ED4AED15}" name="Concept Label Text" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{47B64B06-AAFE-8543-9A00-F21FE128444B}" name="Recommended Definition Text" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{98E3D70A-2524-644A-852E-56E9C2486A77}" name="Source Definition" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{020D7F23-A82E-534F-AC8B-607876DDDA5B}" name="Source Definition ID" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{8827E3BD-F359-2D4D-93BA-19D1AAC81AA3}" name="Date approval of experts recommendations by the PGO steering committee [YYYY-MM-DD]" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{6C8AF982-573E-4F42-A3ED-E79F3399089C}" name="Attribution text" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{51B7F749-BA2F-5042-B34C-A4A1DB0A5929}" name="URL recommended definition" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{2D7BA063-8095-9640-A452-EA7ECF12740E}" name="Examples of sources (these are  not yet  recommended sources)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -881,7 +894,7 @@
     <col min="3" max="3" width="24.5" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" customWidth="1"/>
     <col min="5" max="5" width="24.1640625" customWidth="1"/>
-    <col min="6" max="6" width="47.5" customWidth="1"/>
+    <col min="6" max="6" width="69.5" customWidth="1"/>
     <col min="7" max="7" width="42.33203125" customWidth="1"/>
     <col min="8" max="8" width="49.83203125" customWidth="1"/>
   </cols>
@@ -891,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -929,429 +942,429 @@
         <v>11</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="93" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="104" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="F6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="82" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="83" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="82" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="179" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="173" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1589,15 +1602,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="09548152-9b4f-4597-908e-64737ec281cc">
@@ -1608,14 +1612,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F08AAFC-68EE-427B-A191-69AE331EC991}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F08AAFC-68EE-427B-A191-69AE331EC991}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="09548152-9b4f-4597-908e-64737ec281cc"/>
+    <ds:schemaRef ds:uri="ad920d59-6a69-4911-ba86-f4839e8b8880"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92B9910D-EBDF-40F6-BB4C-CAD0FE1852B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2B69733-670E-400D-858C-C4FDE1B288FF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09548152-9b4f-4597-908e-64737ec281cc"/>
+    <ds:schemaRef ds:uri="ad920d59-6a69-4911-ba86-f4839e8b8880"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2B69733-670E-400D-858C-C4FDE1B288FF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92B9910D-EBDF-40F6-BB4C-CAD0FE1852B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/PGO_V1.0_core_concepts_2026-03-05.xlsx
+++ b/PGO_V1.0_core_concepts_2026-03-05.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanninisato/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanninisato/Documents/GitHub/Pistoia-Alliance-Inc-PGO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C86A90F-59DE-374B-8F21-592F6E40593E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E0DA70-2554-024A-8BDD-0D36D0055D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="110">
   <si>
     <t>Concept Label Text</t>
   </si>
@@ -356,68 +356,52 @@
     <t>Recommended Definition Text</t>
   </si>
   <si>
+    <t>Source attribution: Ontology for Biomedical Investigations (OBI)
+Licence: CC BY 4.0 
+URL licence: https://creativecommons.org/licenses/by/4.0/deed.en 
+Definition accessed on the date: 2025-06-02</t>
+  </si>
+  <si>
     <t>Source attribution: NCI-Thesaurus (NCIT) 
- licence: CC BY 4.0 
- URL licence: https://creativecommons.org/licenses/by/4.0/deed.en
+Licence: CC BY 4.0 
+URL licence: https://creativecommons.org/licenses/by/4.0/deed.en
 Definition accessed on the date: 2025-05-30</t>
   </si>
   <si>
-    <t>Source attribution: Ontology for Biomedical Investigations (OBI)
- licence: CC BY 4.0 
- URL licence: https://creativecommons.org/licenses/by/4.0/deed.en 
- Definition accessed on the date: 2025-06-02</t>
-  </si>
-  <si>
     <t>Source attribution: NCI-Thesaurus (NCIT) 
-licence: CC BY 4.0 
- URL licence: https://creativecommons.org/licenses/by/4.0/deed.en
+Licence: CC BY 4.0 
+URL licence: https://creativecommons.org/licenses/by/4.0/deed.en 
 Definition accessed on the date: 2025-05-30</t>
   </si>
   <si>
-    <t>Source attribution: NCI-Thesaurus (NCIT) 
- licence: CC BY 4.0 
- URL licence: https://creativecommons.org/licenses/by/4.0/deed.en 
- Definition accessed on the date: 2025-05-30</t>
-  </si>
-  <si>
-    <t>Source attribution: NCI-Thesaurus (NCIT) 
- licence: CC BY 4.0 
- URL licence: https://creativecommons.org/licenses/by/4.0/deed.en
- Definition accessed on the date: 2025-05-30</t>
-  </si>
-  <si>
     <t>Source attribution: National Library of Medicine (NLM) - MESH 
- licence: Free access with clear attribution to NLM. 
- URL licence: https://www.nlm.nih.gov/databases/download/terms_and_conditions_mesh.html
+Licence: Free access with clear attribution to NLM. 
+URL licence: https://www.nlm.nih.gov/databases/download/terms_and_conditions_mesh.html
 Definition accessed on the date: 2025-05-30</t>
   </si>
   <si>
     <t>Source attribution: Chemical Entities of Biological Interest (ChEBI) 
- licence: CC BY 4.0 
- URL licence: https://creativecommons.org/licenses/by/4.0/deed.en
- Definition accessed on the date: 2025-06-09</t>
-  </si>
-  <si>
-    <t>Source attribution: Molecular Interactions (MI) - licence: CC BY 4.0 - URL licence: https://github.com/HUPO-PSI/psi-mi-CV/blob/master/LICENSE
+Licence: CC BY 4.0 
+URL licence: https://creativecommons.org/licenses/by/4.0/deed.en
 Definition accessed on the date: 2025-06-09</t>
   </si>
   <si>
+    <t>Source attribution: Molecular Interactions (MI)
+Licence: CC BY 4.0
+URL licence: https://creativecommons.org/licenses/by/4.0/deed.en
+Definition accessed on the date: 2025-06-09</t>
+  </si>
+  <si>
     <t>Source attribution: UniProt 
- licence: CC BY 4.0 
- URL licence: https://creativecommons.org/licenses/by/4.0/deed.en
- Definition accessed on the date: 2025-06-09</t>
-  </si>
-  <si>
-    <t>Source attribution: NCI-Thesaurus (NCIT) 
- licence: CC BY 4.0 
- URL licence: https://creativecommons.org/licenses/by/4.0/deed.en 
-Definition accessed on the date: 2025-05-30</t>
+Licence: CC BY 4.0 
+URL licence: https://creativecommons.org/licenses/by/4.0/deed.en
+Definition accessed on the date: 2025-06-09</t>
   </si>
   <si>
     <t>Source attribution: QUDT 
- licence: CC BY 4.0 
+Licence: CC BY 4.0 
 URL licence: https://creativecommons.org/licenses/by/4.0/deed.en
- Definition accessed on the date: 2025-09-09</t>
+Definition accessed on the date: 2025-09-09</t>
   </si>
 </sst>
 </file>
@@ -942,7 +926,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>12</v>
@@ -968,7 +952,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>18</v>
@@ -994,7 +978,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>23</v>
@@ -1020,7 +1004,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>28</v>
@@ -1046,7 +1030,7 @@
         <v>33</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>34</v>
@@ -1072,7 +1056,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>39</v>
@@ -1098,7 +1082,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>44</v>
@@ -1124,7 +1108,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>49</v>
@@ -1150,7 +1134,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>55</v>
@@ -1176,7 +1160,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>61</v>
@@ -1202,7 +1186,7 @@
         <v>33</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>66</v>
@@ -1228,7 +1212,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>71</v>
@@ -1254,7 +1238,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>76</v>
@@ -1280,7 +1264,7 @@
         <v>33</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>82</v>
@@ -1306,7 +1290,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>88</v>
@@ -1332,7 +1316,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>93</v>
@@ -1358,7 +1342,7 @@
         <v>33</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>99</v>
@@ -1602,6 +1586,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="09548152-9b4f-4597-908e-64737ec281cc">
@@ -1610,15 +1603,6 @@
     <TaxCatchAll xmlns="ad920d59-6a69-4911-ba86-f4839e8b8880" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1641,6 +1625,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92B9910D-EBDF-40F6-BB4C-CAD0FE1852B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2B69733-670E-400D-858C-C4FDE1B288FF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1649,12 +1641,4 @@
     <ds:schemaRef ds:uri="ad920d59-6a69-4911-ba86-f4839e8b8880"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92B9910D-EBDF-40F6-BB4C-CAD0FE1852B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>